--- a/agent/schedule/project-data/02_活动依赖/A3-液冷-活动依赖.xlsx
+++ b/agent/schedule/project-data/02_活动依赖/A3-液冷-活动依赖.xlsx
@@ -456,10 +456,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W97"/>
+  <dimension ref="A1:U97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REL_ID</t>
@@ -565,18 +565,8 @@
           <t>PROJECT_SCALE</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>PROJECT_NAME</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>TOTAL_CARD_COUNT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="2" t="n">
         <v>769</v>
       </c>
@@ -668,16 +658,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="2" t="n">
         <v>770</v>
       </c>
@@ -769,16 +751,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="2" t="n">
         <v>771</v>
       </c>
@@ -870,16 +844,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="2" t="n">
         <v>772</v>
       </c>
@@ -971,16 +937,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="2" t="n">
         <v>773</v>
       </c>
@@ -1072,16 +1030,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="2" t="n">
         <v>774</v>
       </c>
@@ -1173,16 +1123,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="2" t="n">
         <v>775</v>
       </c>
@@ -1274,16 +1216,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="2" t="n">
         <v>776</v>
       </c>
@@ -1375,16 +1309,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="2" t="n">
         <v>777</v>
       </c>
@@ -1476,16 +1402,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="11">
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="2" t="n">
         <v>778</v>
       </c>
@@ -1577,16 +1495,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W11" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="12">
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="2" t="n">
         <v>779</v>
       </c>
@@ -1678,16 +1588,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W12" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="13">
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="2" t="n">
         <v>780</v>
       </c>
@@ -1779,16 +1681,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="14">
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="2" t="n">
         <v>781</v>
       </c>
@@ -1880,16 +1774,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W14" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="15">
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="2" t="n">
         <v>782</v>
       </c>
@@ -1981,16 +1867,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W15" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="16">
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="2" t="n">
         <v>783</v>
       </c>
@@ -2082,16 +1960,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W16" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="17">
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="2" t="n">
         <v>784</v>
       </c>
@@ -2183,16 +2053,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W17" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="18">
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="2" t="n">
         <v>785</v>
       </c>
@@ -2284,16 +2146,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W18" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="19">
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="2" t="n">
         <v>786</v>
       </c>
@@ -2385,16 +2239,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="20">
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="2" t="n">
         <v>787</v>
       </c>
@@ -2486,16 +2332,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W20" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="21">
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" s="2" t="n">
         <v>788</v>
       </c>
@@ -2587,16 +2425,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W21" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="22">
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" s="2" t="n">
         <v>789</v>
       </c>
@@ -2688,16 +2518,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W22" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="23">
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" s="2" t="n">
         <v>790</v>
       </c>
@@ -2789,16 +2611,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W23" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="24">
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" s="2" t="n">
         <v>791</v>
       </c>
@@ -2890,16 +2704,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W24" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="25">
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" s="2" t="n">
         <v>792</v>
       </c>
@@ -2991,16 +2797,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W25" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="26">
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" s="2" t="n">
         <v>793</v>
       </c>
@@ -3092,16 +2890,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W26" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="27">
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" s="2" t="n">
         <v>794</v>
       </c>
@@ -3193,16 +2983,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W27" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="28">
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" s="2" t="n">
         <v>795</v>
       </c>
@@ -3294,16 +3076,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W28" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="29">
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" s="2" t="n">
         <v>796</v>
       </c>
@@ -3395,16 +3169,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W29" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="30">
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" s="2" t="n">
         <v>797</v>
       </c>
@@ -3496,16 +3262,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W30" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="31">
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" s="2" t="n">
         <v>798</v>
       </c>
@@ -3597,16 +3355,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W31" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="32">
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32" s="2" t="n">
         <v>799</v>
       </c>
@@ -3698,16 +3448,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W32" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="33">
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33" s="2" t="n">
         <v>800</v>
       </c>
@@ -3799,16 +3541,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W33" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="34">
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" s="2" t="n">
         <v>801</v>
       </c>
@@ -3900,16 +3634,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W34" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="35">
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" s="2" t="n">
         <v>802</v>
       </c>
@@ -4001,16 +3727,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W35" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="36">
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" s="2" t="n">
         <v>803</v>
       </c>
@@ -4102,16 +3820,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W36" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="37">
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37" s="2" t="n">
         <v>804</v>
       </c>
@@ -4203,16 +3913,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="38">
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38" s="2" t="n">
         <v>805</v>
       </c>
@@ -4304,16 +4006,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W38" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="39">
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39" s="2" t="n">
         <v>806</v>
       </c>
@@ -4405,16 +4099,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W39" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="40">
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40" s="2" t="n">
         <v>807</v>
       </c>
@@ -4506,16 +4192,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W40" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="41">
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" s="2" t="n">
         <v>808</v>
       </c>
@@ -4607,16 +4285,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W41" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="42">
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" s="2" t="n">
         <v>809</v>
       </c>
@@ -4708,16 +4378,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W42" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="43">
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" s="2" t="n">
         <v>810</v>
       </c>
@@ -4809,16 +4471,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W43" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="44">
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" s="2" t="n">
         <v>811</v>
       </c>
@@ -4910,16 +4564,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W44" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="45">
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" s="2" t="n">
         <v>812</v>
       </c>
@@ -5011,16 +4657,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W45" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="46">
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46" s="2" t="n">
         <v>813</v>
       </c>
@@ -5112,16 +4750,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W46" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="47">
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" s="2" t="n">
         <v>814</v>
       </c>
@@ -5213,16 +4843,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W47" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="48">
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48" s="2" t="n">
         <v>815</v>
       </c>
@@ -5314,16 +4936,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W48" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="49">
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" s="2" t="n">
         <v>816</v>
       </c>
@@ -5415,16 +5029,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W49" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="50">
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50" s="2" t="n">
         <v>817</v>
       </c>
@@ -5516,16 +5122,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W50" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51" s="2" t="n">
         <v>818</v>
       </c>
@@ -5617,16 +5215,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W51" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="52">
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52" s="2" t="n">
         <v>819</v>
       </c>
@@ -5718,16 +5308,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W52" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="53">
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" s="2" t="n">
         <v>820</v>
       </c>
@@ -5819,16 +5401,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W53" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="54">
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54" s="2" t="n">
         <v>821</v>
       </c>
@@ -5920,16 +5494,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W54" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="55">
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55" s="2" t="n">
         <v>822</v>
       </c>
@@ -6021,16 +5587,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W55" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="56">
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56" s="2" t="n">
         <v>823</v>
       </c>
@@ -6122,16 +5680,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W56" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="57">
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57" s="2" t="n">
         <v>824</v>
       </c>
@@ -6223,16 +5773,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W57" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="58">
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58" s="2" t="n">
         <v>825</v>
       </c>
@@ -6324,16 +5866,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W58" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="59">
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59" s="2" t="n">
         <v>826</v>
       </c>
@@ -6425,16 +5959,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W59" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="60">
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60" s="2" t="n">
         <v>827</v>
       </c>
@@ -6526,16 +6052,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W60" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="61">
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61" s="2" t="n">
         <v>828</v>
       </c>
@@ -6627,16 +6145,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W61" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="62">
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62" s="2" t="n">
         <v>829</v>
       </c>
@@ -6728,16 +6238,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W62" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="63">
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" s="2" t="n">
         <v>830</v>
       </c>
@@ -6829,16 +6331,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W63" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="64">
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64" s="2" t="n">
         <v>831</v>
       </c>
@@ -6930,16 +6424,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W64" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="65">
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65" s="2" t="n">
         <v>832</v>
       </c>
@@ -7031,16 +6517,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W65" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="66">
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66" s="2" t="n">
         <v>833</v>
       </c>
@@ -7132,16 +6610,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W66" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="67">
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67" s="2" t="n">
         <v>834</v>
       </c>
@@ -7233,16 +6703,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W67" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="68">
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68" s="2" t="n">
         <v>835</v>
       </c>
@@ -7334,16 +6796,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W68" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="69">
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69" s="2" t="n">
         <v>836</v>
       </c>
@@ -7435,16 +6889,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W69" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="70">
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70" s="2" t="n">
         <v>837</v>
       </c>
@@ -7536,16 +6982,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W70" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71" s="2" t="n">
         <v>838</v>
       </c>
@@ -7637,16 +7075,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W71" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="72">
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72" s="2" t="n">
         <v>839</v>
       </c>
@@ -7738,16 +7168,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W72" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="73">
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73" s="2" t="n">
         <v>840</v>
       </c>
@@ -7839,16 +7261,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W73" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="74">
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74" s="2" t="n">
         <v>841</v>
       </c>
@@ -7940,16 +7354,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W74" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="75">
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75" s="2" t="n">
         <v>842</v>
       </c>
@@ -8041,16 +7447,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W75" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="76">
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76" s="2" t="n">
         <v>843</v>
       </c>
@@ -8142,16 +7540,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W76" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="77">
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77" s="2" t="n">
         <v>844</v>
       </c>
@@ -8243,16 +7633,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W77" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="78">
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78" s="2" t="n">
         <v>845</v>
       </c>
@@ -8344,16 +7726,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W78" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="79">
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79" s="2" t="n">
         <v>846</v>
       </c>
@@ -8445,16 +7819,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W79" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="80">
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80" s="2" t="n">
         <v>847</v>
       </c>
@@ -8546,16 +7912,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W80" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="81">
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81" s="2" t="n">
         <v>848</v>
       </c>
@@ -8647,16 +8005,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W81" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="82">
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82" s="2" t="n">
         <v>849</v>
       </c>
@@ -8748,16 +8098,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W82" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="83">
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83" s="2" t="n">
         <v>850</v>
       </c>
@@ -8849,16 +8191,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W83" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="84">
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84" s="2" t="n">
         <v>851</v>
       </c>
@@ -8950,16 +8284,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W84" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="85">
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85" s="2" t="n">
         <v>852</v>
       </c>
@@ -9051,16 +8377,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W85" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="86">
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86" s="2" t="n">
         <v>853</v>
       </c>
@@ -9152,16 +8470,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W86" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="87">
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87" s="2" t="n">
         <v>854</v>
       </c>
@@ -9253,16 +8563,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W87" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="88">
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88" s="2" t="n">
         <v>855</v>
       </c>
@@ -9354,16 +8656,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W88" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="89">
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89" s="2" t="n">
         <v>856</v>
       </c>
@@ -9455,16 +8749,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W89" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="90">
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90" s="2" t="n">
         <v>857</v>
       </c>
@@ -9556,16 +8842,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W90" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="91">
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91" s="2" t="n">
         <v>858</v>
       </c>
@@ -9657,16 +8935,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W91" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="92">
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92" s="2" t="n">
         <v>859</v>
       </c>
@@ -9758,16 +9028,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W92" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="93">
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93" s="2" t="n">
         <v>860</v>
       </c>
@@ -9859,16 +9121,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W93" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="94">
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94" s="2" t="n">
         <v>861</v>
       </c>
@@ -9960,16 +9214,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W94" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="95">
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95" s="2" t="n">
         <v>862</v>
       </c>
@@ -10061,16 +9307,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W95" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="96">
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96" s="2" t="n">
         <v>863</v>
       </c>
@@ -10162,16 +9400,8 @@
           <t>标准项目</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W96" t="n">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="97">
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97" s="2" t="n">
         <v>864</v>
       </c>
@@ -10262,14 +9492,6 @@
         <is>
           <t>标准项目</t>
         </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>A3液冷集群集成</t>
-        </is>
-      </c>
-      <c r="W97" t="n">
-        <v>3456</v>
       </c>
     </row>
   </sheetData>
